--- a/Analysis/03_Hypothesis_Tests/4_H3_outcome_prediction.xlsx
+++ b/Analysis/03_Hypothesis_Tests/4_H3_outcome_prediction.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.08006935331462195</v>
+        <v>-0.09196646867070224</v>
       </c>
       <c r="D7" t="n">
         <v>-1</v>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.07781401010168576</v>
+        <v>-0.08483231166313665</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9996978167258443</v>
+        <v>-0.9950643398554557</v>
       </c>
       <c r="E14" t="n">
-        <v>2.806892810424338e-98</v>
+        <v>6.489313817928521e-62</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.02500773219897945</v>
+        <v>-0.008683842842002187</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2378434187001083</v>
+        <v>0.2084812772279721</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06267666069029224</v>
+        <v>0.1039287283151891</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.03305563020693381</v>
+        <v>-0.03305563020693314</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
